--- a/docs/테스트설계_포트폴리오용.xlsx
+++ b/docs/테스트설계_포트폴리오용.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlim\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlim\OneDrive\Desktop\QATEST\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11AF215-B658-413C-BB8D-79B59EE90B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA059B1-943F-4CB8-90D3-629D2FFCEEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="659" activeTab="6" xr2:uid="{49015EC0-97E5-4CAE-B2C7-8C0F1EDECD8D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="659" firstSheet="3" activeTab="9" xr2:uid="{49015EC0-97E5-4CAE-B2C7-8C0F1EDECD8D}"/>
   </bookViews>
   <sheets>
     <sheet name="마켓컬리_테스트시나리오" sheetId="7" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="631">
   <si>
     <t>TC-ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2490,6 +2490,10 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Check</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2621,7 +2625,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2711,19 +2715,28 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -2734,14 +2747,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3385,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB2BB72-8F51-44F1-B10B-9D07166DD192}">
-  <dimension ref="B1:E15"/>
+  <dimension ref="B1:F15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -3393,10 +3399,11 @@
     <col min="3" max="3" width="24.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.796875" style="14" customWidth="1"/>
     <col min="5" max="5" width="45.296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="13" t="s">
         <v>43</v>
       </c>
@@ -3409,8 +3416,11 @@
       <c r="E2" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F2" s="15" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>438</v>
       </c>
@@ -3423,8 +3433,11 @@
       <c r="E3" s="17" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="F3" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>439</v>
       </c>
@@ -3437,8 +3450,11 @@
       <c r="E4" s="7" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F4" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>440</v>
       </c>
@@ -3451,8 +3467,11 @@
       <c r="E5" s="7" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>441</v>
       </c>
@@ -3465,8 +3484,11 @@
       <c r="E6" s="7" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F6" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>442</v>
       </c>
@@ -3479,8 +3501,11 @@
       <c r="E7" s="7" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>443</v>
       </c>
@@ -3493,8 +3518,11 @@
       <c r="E8" s="7" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
         <v>444</v>
       </c>
@@ -3507,8 +3535,11 @@
       <c r="E9" s="7" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
         <v>445</v>
       </c>
@@ -3521,8 +3552,11 @@
       <c r="E10" s="7" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>446</v>
       </c>
@@ -3535,8 +3569,11 @@
       <c r="E11" s="7" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>447</v>
       </c>
@@ -3549,8 +3586,11 @@
       <c r="E12" s="7" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
         <v>448</v>
       </c>
@@ -3563,8 +3603,11 @@
       <c r="E13" s="7" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
         <v>448</v>
       </c>
@@ -3577,10 +3620,14 @@
       <c r="E14" s="7" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3628,11 +3675,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>$A$1</formula>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>$A$1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+      <formula>$A$1</formula>
       <formula>$A$1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5157,7 +5204,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A540873-FE17-4FE0-8C70-619D2BDE8E77}">
-  <dimension ref="B1:E27"/>
+  <dimension ref="B1:F27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -5165,10 +5212,11 @@
     <col min="3" max="3" width="24.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="55.796875" style="14" customWidth="1"/>
     <col min="5" max="5" width="45.296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="13" t="s">
         <v>43</v>
       </c>
@@ -5181,8 +5229,11 @@
       <c r="E2" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="F2" s="15" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>82</v>
       </c>
@@ -5195,8 +5246,11 @@
       <c r="E3" s="17" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="F3" s="28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
         <v>120</v>
       </c>
@@ -5209,8 +5263,11 @@
       <c r="E4" s="7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F4" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>124</v>
       </c>
@@ -5223,8 +5280,11 @@
       <c r="E5" s="7" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>125</v>
       </c>
@@ -5237,8 +5297,11 @@
       <c r="E6" s="7" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="F6" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>126</v>
       </c>
@@ -5251,8 +5314,11 @@
       <c r="E7" s="7" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>127</v>
       </c>
@@ -5265,8 +5331,11 @@
       <c r="E8" s="7" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
         <v>128</v>
       </c>
@@ -5279,8 +5348,11 @@
       <c r="E9" s="7" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
         <v>129</v>
       </c>
@@ -5293,8 +5365,11 @@
       <c r="E10" s="7" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>130</v>
       </c>
@@ -5307,8 +5382,11 @@
       <c r="E11" s="7" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>207</v>
       </c>
@@ -5321,8 +5399,11 @@
       <c r="E12" s="7" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
         <v>230</v>
       </c>
@@ -5335,8 +5416,11 @@
       <c r="E13" s="7" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
         <v>233</v>
       </c>
@@ -5349,8 +5433,11 @@
       <c r="E14" s="7" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="3" t="s">
         <v>235</v>
       </c>
@@ -5363,8 +5450,11 @@
       <c r="E15" s="7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F15" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="3" t="s">
         <v>265</v>
       </c>
@@ -5377,8 +5467,11 @@
       <c r="E16" s="7" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F16" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
         <v>269</v>
       </c>
@@ -5391,8 +5484,11 @@
       <c r="E17" s="7" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F17" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="3" t="s">
         <v>284</v>
       </c>
@@ -5405,8 +5501,11 @@
       <c r="E18" s="7" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F18" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="3" t="s">
         <v>328</v>
       </c>
@@ -5419,8 +5518,11 @@
       <c r="E19" s="7" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F19" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
         <v>329</v>
       </c>
@@ -5433,8 +5535,11 @@
       <c r="E20" s="7" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F20" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
         <v>330</v>
       </c>
@@ -5447,8 +5552,11 @@
       <c r="E21" s="7" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F21" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="3" t="s">
         <v>331</v>
       </c>
@@ -5461,8 +5569,11 @@
       <c r="E22" s="7" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F22" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="3" t="s">
         <v>332</v>
       </c>
@@ -5475,8 +5586,11 @@
       <c r="E23" s="7" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F23" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="3" t="s">
         <v>333</v>
       </c>
@@ -5489,8 +5603,11 @@
       <c r="E24" s="7" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F24" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="3" t="s">
         <v>387</v>
       </c>
@@ -5503,8 +5620,11 @@
       <c r="E25" s="7" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F25" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="3" t="s">
         <v>617</v>
       </c>
@@ -5517,10 +5637,14 @@
       <c r="E26" s="7" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F26" s="29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/docs/테스트설계_포트폴리오용.xlsx
+++ b/docs/테스트설계_포트폴리오용.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlim\OneDrive\Desktop\QATEST\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA059B1-943F-4CB8-90D3-629D2FFCEEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A0AA32-C32D-4DD4-ADE4-CC4666C98483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="659" firstSheet="3" activeTab="9" xr2:uid="{49015EC0-97E5-4CAE-B2C7-8C0F1EDECD8D}"/>
+    <workbookView xWindow="3780" yWindow="2556" windowWidth="25752" windowHeight="14784" tabRatio="659" firstSheet="2" activeTab="2" xr2:uid="{49015EC0-97E5-4CAE-B2C7-8C0F1EDECD8D}"/>
   </bookViews>
   <sheets>
-    <sheet name="마켓컬리_테스트시나리오" sheetId="7" r:id="rId1"/>
-    <sheet name="마켓컬리_TC" sheetId="4" r:id="rId2"/>
-    <sheet name="마켓컬리_EdgeCases" sheetId="9" r:id="rId3"/>
-    <sheet name="마켓컬리_Risk" sheetId="10" r:id="rId4"/>
-    <sheet name="마켓컬리_StakeholderQuestions" sheetId="11" r:id="rId5"/>
-    <sheet name="API_테스트시나리오" sheetId="13" r:id="rId6"/>
-    <sheet name="API_TC" sheetId="12" r:id="rId7"/>
-    <sheet name="API_EdgeCases " sheetId="14" r:id="rId8"/>
-    <sheet name="API_Risk" sheetId="15" r:id="rId9"/>
-    <sheet name="API_StakeholderQuestions" sheetId="16" r:id="rId10"/>
-    <sheet name="데이터" sheetId="17" state="hidden" r:id="rId11"/>
+    <sheet name="수행율" sheetId="18" r:id="rId1"/>
+    <sheet name="마켓컬리_테스트시나리오" sheetId="7" r:id="rId2"/>
+    <sheet name="마켓컬리_TC" sheetId="4" r:id="rId3"/>
+    <sheet name="마켓컬리_EdgeCases" sheetId="9" r:id="rId4"/>
+    <sheet name="마켓컬리_Risk" sheetId="10" r:id="rId5"/>
+    <sheet name="마켓컬리_StakeholderQuestions" sheetId="11" r:id="rId6"/>
+    <sheet name="API_테스트시나리오" sheetId="13" r:id="rId7"/>
+    <sheet name="API_TC" sheetId="12" r:id="rId8"/>
+    <sheet name="API_EdgeCases " sheetId="14" r:id="rId9"/>
+    <sheet name="API_Risk" sheetId="15" r:id="rId10"/>
+    <sheet name="API_StakeholderQuestions" sheetId="16" r:id="rId11"/>
+    <sheet name="데이터" sheetId="17" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="PFNAB_List">데이터!$A$1:$A$4</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="657">
   <si>
     <t>TC-ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -470,10 +471,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>검색창 진입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. "과" 입력
 2. 자동완성 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -611,10 +608,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>검색 기록 존재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 최근 검색어 목록 표시</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -740,10 +733,6 @@
   </si>
   <si>
     <t>카테고리 필터 노출 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검색 완료 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -877,10 +866,6 @@
   </si>
   <si>
     <t>잘못된 로그인 실패 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 접속 완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -998,14 +983,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상품 상세 페이지 진입 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마켓컬리 홈페이지 접속 성공</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. '장바구니 담기' 버튼 클릭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1133,10 +1110,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>로그인 상태 유지됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 마이페이지 버튼 클릭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1186,10 +1159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>메인 페이지 진입 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. "과자" 검색
 2. 상품 카드에서 [+]버튼 노출 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1207,10 +1176,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상품 수량 UI 노출됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. [+]버튼 2회 클릭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1223,10 +1188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>수량 3 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2. [-]버튼 2회 클릭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1235,16 +1196,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>수량 조절 후 상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. [장바구니 담기] 클릭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 장바구니에 상품 추가됨
-2. 우측 상단에 확인 메시지 노출</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1424,16 +1376,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 홈 화면 이동
-2. 로그인 버튼 표시됨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상품 이미지 정상 로딩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검색 결과 노출 상태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1446,10 +1389,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>해상도 모바일 설정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 모바일 뷰에서 검색창 확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1463,10 +1402,6 @@
   </si>
   <si>
     <t>모바일 장바구니 버튼 위치 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모바일 해상도 적용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2494,6 +2429,163 @@
   </si>
   <si>
     <t>Check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 마켓컬리 홈페이지 접속 성공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 검색창 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 검색 기록 존재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 검색 완료 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 메인 접속 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 상품 상세 페이지 진입 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 마켓컬리 메인 페이지 접속</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 로그인 상태 유지됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 메인 페이지 진입 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 상품 수량 UI 노출됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 수량 3 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 수량 조절 후 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 로그인 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 검색 결과 노출 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 해상도 모바일 설정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 모바일 해상도 적용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 홈 화면으로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 장바구니에 상품 추가됨
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사전 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>총 항목</t>
+  </si>
+  <si>
+    <t>검증항목</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>BLOCK</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>성공율</t>
+  </si>
+  <si>
+    <t>결함율</t>
+  </si>
+  <si>
+    <t>수행율</t>
+  </si>
+  <si>
+    <t>API_TC</t>
+  </si>
+  <si>
+    <t>전체</t>
+  </si>
+  <si>
+    <t>마켓컬리_TC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발생 가능성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시나리오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 케이스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화 파일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2501,7 +2593,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2569,8 +2661,47 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft GothicNeo"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft GothicNeo"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft GothicNeo"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2580,6 +2711,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2625,7 +2780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2683,12 +2838,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2707,14 +2856,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <extLst>
@@ -2730,6 +2871,77 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3097,291 +3309,168 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AFA54B-2571-45B6-9BD1-B6172B50E2C4}">
-  <dimension ref="B1:F22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E7C536-C125-413A-9F1E-ACB28228FF34}">
+  <dimension ref="B2:K5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.796875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="32.59765625" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.09765625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" customWidth="1"/>
+    <col min="3" max="3" width="14.09765625" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" customWidth="1"/>
+    <col min="5" max="5" width="10.8984375" customWidth="1"/>
+    <col min="6" max="6" width="11.296875" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="11.69921875" customWidth="1"/>
+    <col min="10" max="10" width="14.8984375" customWidth="1"/>
+    <col min="11" max="11" width="15.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B2" s="27" t="s">
+        <v>638</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>639</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>640</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>641</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>642</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>643</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>644</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>645</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B3" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="C3" s="29">
+        <f ca="1">COUNTA(INDIRECT("'"&amp;B3&amp;"'!B3:B100"))</f>
+        <v>21</v>
+      </c>
+      <c r="D3" s="29">
+        <f ca="1">COUNTIFS(INDIRECT("'"&amp;B3&amp;"'!K3:K100"),"&lt;&gt;")</f>
+        <v>5</v>
+      </c>
+      <c r="E3" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B3&amp;"'!K3:K100"),"P")</f>
+        <v>4</v>
+      </c>
+      <c r="F3" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B3&amp;"'!K3:K100"),"F")</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B3&amp;"'!K3:K100"),"B")</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B3&amp;"'!K3:K100"),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="30" t="str">
+        <f ca="1">IF(D3=0, "0%", ROUND((E3/D3*100),0)&amp;"%")</f>
+        <v>80%</v>
+      </c>
+      <c r="J3" s="30" t="str">
+        <f ca="1">IF(D3=0,"0%",ROUND((F3/D3*100),0)&amp;"%")</f>
+        <v>20%</v>
+      </c>
+      <c r="K3" s="30" t="str">
+        <f ca="1">IF(D3=0,"0%",ROUND((D3/C3*100),0)&amp;"%")</f>
+        <v>24%</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B4" s="28" t="s">
+        <v>648</v>
+      </c>
+      <c r="C4" s="29">
+        <f ca="1">COUNTA(INDIRECT("'"&amp;B4&amp;"'!B3:B100"))</f>
+        <v>9</v>
+      </c>
+      <c r="D4" s="29">
+        <f ca="1">COUNTIFS(INDIRECT("'"&amp;B4&amp;"'!K3:K100"),"&lt;&gt;")</f>
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E4" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B4&amp;"'!K3:K100"),"P")</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B4&amp;"'!K3:K100"),"F")</f>
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="G4" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B4&amp;"'!K3:K100"),"B")</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="29">
+        <f ca="1">COUNTIF(INDIRECT("'"&amp;B4&amp;"'!K3:K100"),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="30" t="str">
+        <f ca="1">IF(D4=0, "0%", ROUND((E4/D4*100),0)&amp;"%")</f>
+        <v>67%</v>
+      </c>
+      <c r="J4" s="30" t="str">
+        <f ca="1">IF(D4=0,"0%",ROUND((F4/D4*100),0)&amp;"%")</f>
+        <v>33%</v>
+      </c>
+      <c r="K4" s="30" t="str">
+        <f ca="1">IF(D4=0,"0%",ROUND((D4/C4*100),0)&amp;"%")</f>
+        <v>33%</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B5" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="C5" s="29">
+        <f ca="1">SUM(C3:C4)</f>
+        <v>30</v>
+      </c>
+      <c r="D5" s="29">
+        <f t="shared" ref="D5:H5" ca="1" si="0">SUM(D3:D4)</f>
+        <v>8</v>
+      </c>
+      <c r="E5" s="29">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="E22" s="26"/>
+      <c r="F5" s="29">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="29">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="29">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3390,8 +3479,249 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C49C79-DB97-4E06-9DD7-BBBDB5E712AC}">
+  <dimension ref="B1:F14"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.8984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.796875" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B3" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B4" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B5" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B6" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B7" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B8" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B9" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B10" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B12" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B13" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B14" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>566</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB2BB72-8F51-44F1-B10B-9D07166DD192}">
-  <dimension ref="B1:F15"/>
+  <dimension ref="B1:G15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -3402,8 +3732,8 @@
     <col min="6" max="6" width="6.5" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:7" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="13" t="s">
         <v>43</v>
       </c>
@@ -3417,214 +3747,217 @@
         <v>46</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>435</v>
+      </c>
+      <c r="F3" s="25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="B4" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="F3" s="28" t="b">
+      <c r="F4" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F4" s="29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F5" s="29" t="b">
+        <v>459</v>
+      </c>
+      <c r="F5" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="F6" s="29" t="b">
+        <v>461</v>
+      </c>
+      <c r="F6" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="F7" s="29" t="b">
+        <v>463</v>
+      </c>
+      <c r="F7" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="F8" s="29" t="b">
+        <v>488</v>
+      </c>
+      <c r="F8" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="F9" s="29" t="b">
+        <v>490</v>
+      </c>
+      <c r="F9" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="F10" s="29" t="b">
+        <v>492</v>
+      </c>
+      <c r="F10" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="F11" s="29" t="b">
+        <v>520</v>
+      </c>
+      <c r="F11" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="F12" s="29" t="b">
+        <v>522</v>
+      </c>
+      <c r="F12" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="F13" s="29" t="b">
+        <v>524</v>
+      </c>
+      <c r="F13" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="F14" s="29" t="b">
+        <v>606</v>
+      </c>
+      <c r="F14" s="26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
@@ -3635,41 +3968,47 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175D888A-C9C1-47C2-A885-0D1F477E14EA}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>625</v>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
+        <v>609</v>
       </c>
       <c r="C1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="22" t="s">
-        <v>627</v>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="20" t="s">
+        <v>611</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="23" t="s">
-        <v>628</v>
+      <c r="E2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>612</v>
       </c>
       <c r="C3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="24" t="s">
-        <v>629</v>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -3696,6 +4035,299 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AFA54B-2571-45B6-9BD1-B6172B50E2C4}">
+  <dimension ref="B1:F22"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.796875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="32.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.09765625" style="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B3" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B4" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B5" s="36" t="s">
+        <v>595</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B7" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B8" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>594</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B9" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="36" t="s">
+        <v>596</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B11" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B12" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B13" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B14" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B15" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B16" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B17" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="E22" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B195D1EC-79D1-4777-93DA-09E7489ACD9C}">
   <dimension ref="B1:K29"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -3706,701 +4338,703 @@
     <col min="4" max="4" width="34.8984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.09765625" style="14" customWidth="1"/>
     <col min="6" max="6" width="36.796875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="7.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="C2" s="31" t="s">
+        <v>634</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>633</v>
+      </c>
+      <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="27" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>636</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>656</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+      <c r="K2" s="27" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="25" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
+      <c r="K3" s="41" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B4" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
+      <c r="J4" s="39" t="s">
+        <v>587</v>
+      </c>
+      <c r="K4" s="41" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B5" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="E5" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="J5" s="39" t="s">
+        <v>587</v>
+      </c>
+      <c r="K5" s="41" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B6" s="37" t="s">
+        <v>572</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="32" t="s">
+        <v>616</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="I6" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="41" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="37" t="s">
+        <v>573</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>617</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H7" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K6" s="25"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="K7" s="25"/>
-    </row>
-    <row r="8" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="C8" s="19" t="s">
+      <c r="K7" s="41"/>
+    </row>
+    <row r="8" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B8" s="37" t="s">
+        <v>574</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="E8" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="J8" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" s="41"/>
+    </row>
+    <row r="9" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B9" s="37" t="s">
+        <v>576</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>618</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>575</v>
+      </c>
+      <c r="K9" s="41"/>
+    </row>
+    <row r="10" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B10" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>618</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H10" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="K8" s="25"/>
-    </row>
-    <row r="9" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="I10" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="J10" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="41"/>
+    </row>
+    <row r="11" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B11" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>619</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>591</v>
-      </c>
-      <c r="K9" s="25"/>
-    </row>
-    <row r="10" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="I11" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" s="41"/>
+    </row>
+    <row r="12" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B12" s="37" t="s">
+        <v>579</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="25"/>
-    </row>
-    <row r="11" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K11" s="25"/>
-    </row>
-    <row r="12" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" s="9" t="str">
+      <c r="H12" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="39" t="str">
         <f>I7</f>
         <v>-</v>
       </c>
-      <c r="J12" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="K12" s="25"/>
-    </row>
-    <row r="13" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="J12" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="K12" s="41"/>
+    </row>
+    <row r="13" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B13" s="37" t="s">
+        <v>580</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>621</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="41"/>
+    </row>
+    <row r="14" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B14" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>622</v>
+      </c>
+      <c r="E14" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="F14" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="G14" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="41"/>
+    </row>
+    <row r="15" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B15" s="37" t="s">
+        <v>582</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>623</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="G15" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H15" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B16" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>624</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="41"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B17" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>625</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" s="41"/>
+    </row>
+    <row r="18" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B18" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>626</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>286</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="41"/>
+    </row>
+    <row r="19" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B19" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>627</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>631</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" s="25"/>
-    </row>
-    <row r="14" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G14" s="9" t="s">
+      <c r="J19" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="41"/>
+    </row>
+    <row r="20" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B20" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="G20" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H20" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="41"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B21" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>629</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="25"/>
-    </row>
-    <row r="15" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="25"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="25"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K17" s="25"/>
-    </row>
-    <row r="18" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" s="25"/>
-    </row>
-    <row r="19" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B19" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="J21" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="K21" s="41"/>
+    </row>
+    <row r="22" spans="2:11" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B22" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>630</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K19" s="25"/>
-    </row>
-    <row r="20" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K20" s="25"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B21" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="9" t="s">
+      <c r="J22" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="K22" s="41"/>
+    </row>
+    <row r="23" spans="2:11" ht="41.4" x14ac:dyDescent="0.4">
+      <c r="B23" s="37" t="s">
+        <v>589</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>590</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="25"/>
-    </row>
-    <row r="22" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="K22" s="25"/>
-    </row>
-    <row r="23" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="B23" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="J23" s="39" t="s">
+        <v>593</v>
+      </c>
+      <c r="K23" s="41" t="s">
         <v>608</v>
       </c>
-      <c r="G23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>624</v>
-      </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K24" s="24"/>
+      <c r="K24" s="22"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K25" s="24"/>
+      <c r="K25" s="22"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K26" s="24"/>
+      <c r="K26" s="22"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K27" s="24"/>
+      <c r="K27" s="22"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K28" s="24"/>
+      <c r="K28" s="22"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K29" s="24"/>
+      <c r="K29" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4412,12 +5046,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{178FEE8E-0FF3-47B8-B3B1-AE959344737D}">
           <x14:formula1>
             <xm:f>데이터!$C$1:$C$3</xm:f>
           </x14:formula1>
           <xm:sqref>G3:G23</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{454F4399-E377-4F1A-AC53-A28B289056D1}">
+          <x14:formula1>
+            <xm:f>데이터!$E$1:$E$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>H1:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4425,7 +5065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5145AE-7DFA-40DD-99BE-5E7528C85795}">
   <dimension ref="B1:E27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -4434,381 +5074,393 @@
     <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.296875" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.8984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
+      <c r="C2" s="48" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>655</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="39" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="39" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B6" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E6" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B7" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="9" t="s">
+    <row r="8" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B8" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="9" t="s">
+    <row r="9" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B9" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B10" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="9" t="s">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B11" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="9" t="s">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B12" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="9" t="s">
+    <row r="13" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B13" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="9" t="s">
+    <row r="14" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B14" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="E14" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="9" t="s">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B15" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" s="9" t="s">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B16" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="9" t="s">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B18" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="E18" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E15" s="9" t="s">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B19" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B20" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="E20" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E16" s="9" t="s">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B21" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="E21" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E17" s="9" t="s">
+    <row r="22" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B22" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="E22" s="39" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="6" t="s">
+    <row r="23" spans="2:5" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B23" s="44" t="s">
         <v>248</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="C23" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B24" s="44" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="C24" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B19" s="3" t="s">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B25" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
+      <c r="C25" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>352</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B26" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="C26" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="E26" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B21" s="3" t="s">
+    <row r="27" spans="2:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="44" t="s">
         <v>252</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B23" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B24" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B26" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="C27" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="E27" s="39" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{23A31B2D-FB91-49BB-ADF6-08C0D2423C5E}">
+          <x14:formula1>
+            <xm:f>데이터!$C$1:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E35</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF080B24-5DCF-4B0B-9C9F-7F2C7FD4A80A}">
   <dimension ref="B1:F23"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -4817,383 +5469,383 @@
     <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.8984375" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="1" customWidth="1"/>
     <col min="6" max="6" width="36.796875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="D2" s="47" t="s">
+        <v>652</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>651</v>
+      </c>
+      <c r="F2" s="31" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B4" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B5" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B6" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B7" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B8" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B9" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="F9" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="20" t="s">
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B10" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B11" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B12" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B13" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="27.6" x14ac:dyDescent="0.4">
+      <c r="B14" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B15" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="F15" s="34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B16" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E16" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F16" s="34" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="F17" s="34" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B18" s="46" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B19" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B17" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B19" s="3" t="s">
+      <c r="F19" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>377</v>
+      <c r="F20" s="34" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>378</v>
+      <c r="B21" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B22" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>380</v>
+      <c r="B22" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B23" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>382</v>
+      <c r="B23" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -5202,7 +5854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A540873-FE17-4FE0-8C70-619D2BDE8E77}">
   <dimension ref="B1:F27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -5230,7 +5882,7 @@
         <v>46</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="52.2" x14ac:dyDescent="0.4">
@@ -5238,406 +5890,406 @@
         <v>82</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="28" t="b">
+        <v>156</v>
+      </c>
+      <c r="F3" s="25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="29" t="b">
+      <c r="F4" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="29" t="b">
+        <v>168</v>
+      </c>
+      <c r="F5" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="29" t="b">
+      <c r="F6" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F7" s="29" t="b">
+        <v>166</v>
+      </c>
+      <c r="F7" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="29" t="b">
+        <v>163</v>
+      </c>
+      <c r="F8" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F9" s="29" t="b">
+        <v>165</v>
+      </c>
+      <c r="F9" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" s="29" t="b">
+        <v>201</v>
+      </c>
+      <c r="F10" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="29" t="b">
+        <v>203</v>
+      </c>
+      <c r="F11" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" s="29" t="b">
+        <v>206</v>
+      </c>
+      <c r="F12" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="F13" s="29" t="b">
+        <v>228</v>
+      </c>
+      <c r="F13" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F14" s="29" t="b">
+        <v>262</v>
+      </c>
+      <c r="F14" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F15" s="29" t="b">
+        <v>234</v>
+      </c>
+      <c r="F15" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="F16" s="29" t="b">
+        <v>261</v>
+      </c>
+      <c r="F16" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F17" s="29" t="b">
+        <v>265</v>
+      </c>
+      <c r="F17" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="3" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="F18" s="29" t="b">
+        <v>279</v>
+      </c>
+      <c r="F18" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="F19" s="29" t="b">
+        <v>323</v>
+      </c>
+      <c r="F19" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="F20" s="29" t="b">
+        <v>325</v>
+      </c>
+      <c r="F20" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="F21" s="29" t="b">
+        <v>327</v>
+      </c>
+      <c r="F21" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="F22" s="29" t="b">
+        <v>368</v>
+      </c>
+      <c r="F22" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="F23" s="29" t="b">
+        <v>370</v>
+      </c>
+      <c r="F23" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="F24" s="29" t="b">
+        <v>373</v>
+      </c>
+      <c r="F24" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="F25" s="29" t="b">
+        <v>376</v>
+      </c>
+      <c r="F25" s="26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="3" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="F26" s="29" t="b">
+        <v>603</v>
+      </c>
+      <c r="F26" s="26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +6304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0D642C0-6796-4A7F-AA54-32A60A7BF234}">
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -5685,138 +6337,138 @@
     </row>
     <row r="3" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -5825,7 +6477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C28D0B-8FAE-4D21-8CB2-3F6E80349F65}">
   <dimension ref="B1:K27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -5873,54 +6525,56 @@
         <v>14</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>65</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="K3" s="25"/>
+        <v>377</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="4" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>21</v>
@@ -5929,28 +6583,30 @@
         <v>65</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="K4" s="25"/>
+        <v>439</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="5" spans="2:11" ht="52.2" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>21</v>
@@ -5959,28 +6615,28 @@
         <v>65</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="K5" s="25"/>
+        <v>464</v>
+      </c>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" spans="2:11" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>21</v>
@@ -5989,148 +6645,150 @@
         <v>65</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="K6" s="25"/>
+        <v>493</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="7" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="J7" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="K7" s="25"/>
+        <v>525</v>
+      </c>
+      <c r="K7" s="23"/>
     </row>
     <row r="8" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="H8" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="J8" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="K8" s="25"/>
+        <v>526</v>
+      </c>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="J9" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="K9" s="25"/>
+        <v>527</v>
+      </c>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>115</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="K10" s="25"/>
+        <v>527</v>
+      </c>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="2:11" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>562</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>578</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>32</v>
@@ -6139,60 +6797,60 @@
         <v>65</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="K11" s="25"/>
+        <v>563</v>
+      </c>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K12" s="24"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K13" s="24"/>
+      <c r="K13" s="22"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K14" s="24"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K15" s="24"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="K16" s="24"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K17" s="24"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K18" s="24"/>
+      <c r="K18" s="22"/>
     </row>
     <row r="19" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K19" s="24"/>
+      <c r="K19" s="22"/>
     </row>
     <row r="20" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K20" s="24"/>
+      <c r="K20" s="22"/>
     </row>
     <row r="21" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K21" s="24"/>
+      <c r="K21" s="22"/>
     </row>
     <row r="22" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K22" s="24"/>
+      <c r="K22" s="22"/>
     </row>
     <row r="23" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K23" s="24"/>
+      <c r="K23" s="22"/>
     </row>
     <row r="24" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K24" s="24"/>
+      <c r="K24" s="22"/>
     </row>
     <row r="25" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K25" s="24"/>
+      <c r="K25" s="22"/>
     </row>
     <row r="26" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K26" s="24"/>
+      <c r="K26" s="22"/>
     </row>
     <row r="27" spans="11:11" x14ac:dyDescent="0.4">
-      <c r="K27" s="24"/>
+      <c r="K27" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6217,7 +6875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DF7C03-3F41-470D-93D3-FDB158098A65}">
   <dimension ref="B1:E15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
@@ -6246,13 +6904,13 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>21</v>
@@ -6260,13 +6918,13 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B4" s="3" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>32</v>
@@ -6274,13 +6932,13 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>421</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>70</v>
@@ -6288,13 +6946,13 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>32</v>
@@ -6302,13 +6960,13 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>70</v>
@@ -6316,13 +6974,13 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>70</v>
@@ -6330,13 +6988,13 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>32</v>
@@ -6344,13 +7002,13 @@
     </row>
     <row r="10" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>32</v>
@@ -6358,13 +7016,13 @@
     </row>
     <row r="11" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>32</v>
@@ -6372,13 +7030,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>32</v>
@@ -6386,13 +7044,13 @@
     </row>
     <row r="13" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>70</v>
@@ -6400,13 +7058,13 @@
     </row>
     <row r="14" spans="2:5" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>70</v>
@@ -6414,257 +7072,16 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B15" s="3" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C49C79-DB97-4E06-9DD7-BBBDB5E712AC}">
-  <dimension ref="B1:F14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="11.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.796875" style="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" ht="12.45" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B5" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B6" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B7" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B8" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B9" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B10" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B11" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B12" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="B13" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>582</v>
       </c>
     </row>
   </sheetData>
